--- a/教員見回り担当表.xlsx
+++ b/教員見回り担当表.xlsx
@@ -72,7 +72,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -127,11 +127,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E67E22"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008E44AD"/>
       </patternFill>
     </fill>
     <fill>
@@ -274,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -312,9 +307,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -328,24 +320,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1061,20 +1053,20 @@
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>保育・製造工業</t>
+          <t>保育</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園 → 江南市立小鹿保育園 → リスパック株式会社 真空成形工場</t>
+          <t>江南市立藤里保育園</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>14.9km</t>
+          <t>7.2km</t>
         </is>
       </c>
     </row>
@@ -1113,43 +1105,38 @@
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>保育・物流</t>
+          <t>保育・製造工業</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>江南市立藤里保育園 → ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
+          <t>江南市立古知野東保育園 → 江南市立小鹿保育園 → リスパック株式会社 真空成形工場</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>45.9km</t>
+          <t>14.9km</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>7/31(金)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>教員 1</t>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>教員 4</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>保育</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園</t>
+          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
@@ -1157,111 +1144,116 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>18.0km</t>
+          <t>40.6km</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>教員 2</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>7/31(金)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>教員 1</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>製造工業</t>
+          <t>保育</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>東罐興業株式会社　小牧工場</t>
+          <t>江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>12.8km</t>
+          <t>18.0km</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>教員 3</t>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>教員 2</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>製造工業・保育</t>
+          <t>製造工業</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>グンゼ江南工場 → 江南市立宮田東保育園</t>
+          <t>東罐興業株式会社　小牧工場 → 東名化学工業株式会社　小牧工場</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>8.3km</t>
+          <t>22.3km</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>教員 4</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>教員 3</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>物流・製造工業</t>
+          <t>保育・製造工業</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社 → 東名化学工業株式会社　小牧工場</t>
+          <t>江南市立古知野東保育園 → グンゼ江南工場 → 江南市立宮田東保育園</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>26.1km</t>
+          <t>8.4km</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>教員 5</t>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>教員 4</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>保育</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園</t>
+          <t>福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>3.2km</t>
+          <t>9.2km</t>
         </is>
       </c>
     </row>
@@ -1630,16 +1622,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A13:A16"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1663,47 +1655,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　8/27(木)　(6社 / 11名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -1728,8 +1720,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -1739,23 +1731,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>江南市立宮田保育園　　[生徒: 2-1-30・2-2-19]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 1.1km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -1780,26 +1772,26 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 3社 / 6名</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>計 20.5km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -1824,8 +1816,8 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -1835,23 +1827,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>株式会社愛知イエローハット　一宮店　　[生徒: 2-2-16・2-3-7]</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>前より 5.0km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>美容</t>
         </is>
@@ -1876,18 +1868,18 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 3社 / 5名</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr"/>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr"/>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>計 18.3km</t>
         </is>
@@ -1925,47 +1917,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　8/28(金)　(2社 / 5名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -1990,8 +1982,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="21" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2001,33 +1993,33 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>江南市立古知野北保育園　　[生徒: 2-1-4・2-3-2・2-3-4・2-3-9]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 3.3km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 2社 / 5名</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr"/>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>計 7.0km</t>
         </is>
@@ -2062,47 +2054,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　7/27(月)　(8社 / 13名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -2127,8 +2119,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2138,23 +2130,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>江南市立宮田南保育園　　[生徒: 1-5-26]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 1.9km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2179,26 +2171,26 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 3社 / 5名</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>計 14.1km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -2223,8 +2215,8 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2234,41 +2226,41 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>大口屋木賀工場　　[生徒: 1-5-20・1-5-21]</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>前より 2.4km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 2社 / 4名</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr"/>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>計 5.8km</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -2293,8 +2285,8 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2304,23 +2296,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>江南市立藤里保育園　　[生徒: 2-1-36]</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>前より 3.4km</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -2345,18 +2337,18 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>教員 3　計 3社 / 4名</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr"/>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>計 32.1km</t>
         </is>
@@ -2397,47 +2389,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　7/28(火)　(7社 / 12名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2462,8 +2454,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="21" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2473,41 +2465,41 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>大口屋木賀工場　　[生徒: 1-5-29・1-5-37]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 1.8km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 2社 / 3名</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr"/>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>計 6.1km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="16" t="inlineStr"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2532,8 +2524,8 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2543,23 +2535,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>江南市立草井保育園　　[生徒: 1-5-12・1-5-14]</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>前より 1.9km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2584,26 +2576,26 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 3社 / 6名</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr"/>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>計 11.0km</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2628,8 +2620,8 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -2639,33 +2631,33 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>東名化学工業株式会社　小牧工場　　[生徒: 2-1-15・2-4-20]</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>前より 14.3km</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>教員 3　計 2社 / 3名</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr"/>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>計 28.7km</t>
         </is>
@@ -2706,47 +2698,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　7/29(水)　(8社 / 14名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="27" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>美容</t>
         </is>
@@ -2771,26 +2763,26 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 1社 / 1名</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr"/>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr"/>
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>計 17.3km</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="16" t="inlineStr"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2815,8 +2807,8 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2826,23 +2818,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>江南市立布袋西保育園　　[生徒: 1-5-4・1-5-22]</t>
         </is>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>前より 1.8km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>製造食品</t>
         </is>
@@ -2867,26 +2859,26 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 3社 / 5名</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr"/>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>計 7.7km</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="16" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr"/>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -2911,8 +2903,8 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -2922,41 +2914,41 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>江南市立藤里保育園　　[生徒: 2-2-20]</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>前より 2.2km</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>教員 3　計 2社 / 3名</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr"/>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr"/>
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>計 8.6km</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr"/>
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -2981,8 +2973,8 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>物流</t>
         </is>
@@ -2992,33 +2984,33 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>キムラユニティー株式会社　犬山工場　　[生徒: 2-1-1・2-1-19・2-4-14]</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>前より 4.4km</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>教員 4　計 2社 / 5名</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr"/>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>計 10.3km</t>
         </is>
@@ -3049,7 +3041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3061,47 +3053,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　7/30(木)　(8社 / 21名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3113,266 +3105,285 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
+          <t>江南市立藤里保育園　　[生徒: 2-4-7]</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>学校から 3.6km</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>教員 1　計 1社 / 1名</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr"/>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>計 7.2km</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1社目</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>江南市立古知野中保育園　　[生徒: 1-5-18・1-5-39・2-4-3]</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>学校から 2.0km</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2社目</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>江南市立古知野西保育園　　[生徒: 1-5-2・1-5-32]</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>前より 1.9km</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>製造食品</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3社目</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ガレ・ドゥ・ワタナベ　　[生徒: 1-5-33・1-5-38]</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>前より 3.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>教員 2　計 3社 / 7名</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>計 9.7km</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="15" t="inlineStr"/>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1社目</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>江南市立古知野東保育園　　[生徒: 1-5-3・1-5-31]</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>学校から 1.6km</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>江南市立小鹿保育園　　[生徒: 1-5-36・2-2-8]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>前より 2.1km</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="17" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  3社目</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>リスパック株式会社 真空成形工場　　[生徒: 1-5-6・2-1-27・2-1-28・2-3-11・2-3-17]</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>前より 6.3km</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>教員 1　計 3社 / 9名</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>教員 3　計 3社 / 9名</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>計 14.9km</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>保育</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="26" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  1社目</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>江南市立古知野中保育園　　[生徒: 1-5-18・1-5-39・2-4-3]</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>学校から 2.0km</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>保育</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2社目</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>江南市立古知野西保育園　　[生徒: 1-5-2・1-5-32]</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>前より 1.9km</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>製造食品</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3社目</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>ガレ・ドゥ・ワタナベ　　[生徒: 1-5-33・1-5-38]</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>前より 3.3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店　　[生徒: 2-2-9・2-2-11・2-2-15・2-4-12]</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>学校から 20.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>教員 2　計 3社 / 7名</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr"/>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>計 9.7km</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>保育</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1社目</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>江南市立藤里保育園　　[生徒: 2-4-7]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>学校から 3.6km</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2社目</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店　　[生徒: 2-2-9・2-2-11・2-2-15・2-4-12]</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>前より 22.0km</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>教員 3　計 2社 / 5名</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr"/>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>計 45.9km</t>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>教員 4　計 1社 / 4名</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>計 40.6km</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="D11:E11"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3384,7 +3395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3396,47 +3407,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　7/31(金)　(10社 / 20名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3461,8 +3472,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3472,23 +3483,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>江南市立古知野南保育園　　[生徒: 1-5-23・2-1-17]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 1.8km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3513,26 +3524,26 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 3社 / 4名</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>計 18.0km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="27" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -3556,161 +3567,161 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>製造工業</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2社目</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>東名化学工業株式会社　小牧工場　　[生徒: 2-3-8・2-3-13]</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>前より 5.1km</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>教員 2　計 1社 / 1名</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr"/>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>計 12.8km</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="16" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>教員 2　計 2社 / 3名</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>計 22.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1社目</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>江南市立古知野東保育園　　[生徒: 2-4-22]</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>学校から 1.6km</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2社目</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>グンゼ江南工場　　[生徒: 1-5-24・2-1-29・2-1-32・2-3-12・2-3-15]</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>前より 1.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>保育</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3社目</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>江南市立宮田東保育園　　[生徒: 1-5-1・1-5-25]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>前より 1.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>教員 3　計 3社 / 8名</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>計 8.4km</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="15" t="inlineStr"/>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  1社目</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>グンゼ江南工場　　[生徒: 1-5-24・2-1-29・2-1-32・2-3-12・2-3-15]</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>学校から 2.8km</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>保育</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2社目</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>江南市立宮田東保育園　　[生徒: 1-5-1・1-5-25]</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>前より 1.3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>教員 3　計 2社 / 7名</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr"/>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>計 8.3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1社目</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>福玉ロジスティクス株式会社　大口センター　　[生徒: 2-4-18・2-4-25]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>学校から 2.1km</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="18" t="n"/>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2社目</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>株式会社メイコン　本社　　[生徒: 2-1-14・2-2-6・2-4-24]</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>前より 2.5km</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>製造工業</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3社目</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>東名化学工業株式会社　小牧工場　　[生徒: 2-3-8・2-3-13]</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
@@ -3718,88 +3729,69 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>前より 10.7km</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+          <t>学校から 2.1km</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2社目</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>株式会社メイコン　本社　　[生徒: 2-1-14・2-2-6・2-4-24]</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>前より 2.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>教員 4　計 3社 / 7名</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr"/>
-      <c r="F18" s="26" t="inlineStr">
-        <is>
-          <t>計 26.1km</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="27" t="inlineStr"/>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>保育</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1社目</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園　　[生徒: 2-4-22]</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>学校から 1.6km</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>教員 5　計 1社 / 1名</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr"/>
-      <c r="F21" s="26" t="inlineStr">
-        <is>
-          <t>計 3.2km</t>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>教員 4　計 2社 / 5名</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr"/>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>計 9.2km</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B13:C13"/>
+  <mergeCells count="13">
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3823,47 +3815,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　8/24(月)　(8社 / 14名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>美容</t>
         </is>
@@ -3888,8 +3880,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3899,23 +3891,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>江南市立古知野東保育園　　[生徒: 2-4-5・2-4-26]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 2.8km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3940,26 +3932,26 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 3社 / 6名</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>計 9.9km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -3984,8 +3976,8 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -3995,23 +3987,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>江南市立門弟山保育園　　[生徒: 2-1-3・2-3-3]</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>前より 1.3km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -4036,26 +4028,26 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 3社 / 5名</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr"/>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr"/>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>計 8.5km</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="16" t="inlineStr"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr"/>
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -4080,8 +4072,8 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -4091,33 +4083,33 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>江南市立布袋保育園　　[生徒: 2-2-12]</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>前より 0.4km</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>教員 3　計 2社 / 3名</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr"/>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>計 5.7km</t>
         </is>
@@ -4158,47 +4150,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　8/25(火)　(7社 / 15名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -4223,8 +4215,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -4234,23 +4226,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>株式会社東海理化電機製作所　　[生徒: 2-1-34・2-1-35・2-4-29]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 1.9km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -4275,26 +4267,26 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 3社 / 8名</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>計 8.7km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="16" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -4319,8 +4311,8 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -4330,41 +4322,41 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>江南市立宮田東保育園　　[生徒: 2-1-2]</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>前より 1.7km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 2社 / 3名</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr"/>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>計 9.6km</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -4389,8 +4381,8 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>美容</t>
         </is>
@@ -4400,33 +4392,33 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>TJ天気予報 7mm 北名古屋店　　[生徒: 2-1-10・2-1-31]</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>前より 8.9km</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>教員 3　計 2社 / 4名</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr"/>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>計 27.0km</t>
         </is>
@@ -4467,47 +4459,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>見回り担当表　8/26(水)　(8社 / 16名)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>担当教員名</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>業種</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>訪問順</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>訪問先企業</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>生徒数</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -4532,8 +4524,8 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="21" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -4543,41 +4535,41 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>江南市立布袋東保育園　　[生徒: 2-1-24・2-2-10]</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>前より 2.9km</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>教員 1　計 2社 / 4名</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr"/>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>計 8.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="16" t="inlineStr"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>販売</t>
         </is>
@@ -4602,8 +4594,8 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>美容</t>
         </is>
@@ -4613,23 +4605,23 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>サロンド榮　　[生徒: 2-1-26]</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>前より 0.7km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>保育</t>
         </is>
@@ -4654,26 +4646,26 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>教員 2　計 3社 / 5名</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr"/>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>計 19.1km</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="27" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr"/>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -4698,26 +4690,26 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>教員 3　計 1社 / 2名</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr"/>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr"/>
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>計 15.5km</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="16" t="inlineStr"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr"/>
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>美容</t>
         </is>
@@ -4742,8 +4734,8 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>製造工業</t>
         </is>
@@ -4753,33 +4745,33 @@
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>アイカテック建材株式会社名古屋工場　　[生徒: 2-3-5・2-3-19・2-4-17]</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>前より 13.9km</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>教員 4　計 2社 / 5名</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr"/>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>計 38.7km</t>
         </is>

--- a/教員見回り担当表.xlsx
+++ b/教員見回り担当表.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全日程一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="7-27月" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="7-28火" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="7-29水" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="7-30木" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="7-31金" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="8-24月" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8-25火" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8-26水" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="8-27木" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8-28金" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全日程一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-27月" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-28火" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-29水" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-30木" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-31金" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-24月" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-25火" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-26水" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-27木" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-28金" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1214,20 +1214,20 @@
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>保育・製造工業</t>
+          <t>製造工業・保育</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園 → グンゼ江南工場 → 江南市立宮田東保育園</t>
+          <t>グンゼ江南工場 → 江南市立宮田東保育園</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>8.4km</t>
+          <t>8.3km</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3409,7 +3409,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>見回り担当表　7/31(金)　(10社 / 20名)</t>
+          <t>見回り担当表　7/31(金)　(9社 / 19名)</t>
         </is>
       </c>
     </row>
@@ -3615,163 +3615,137 @@
       <c r="A12" s="15" t="inlineStr"/>
       <c r="B12" s="16" t="inlineStr">
         <is>
+          <t>製造工業</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1社目</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>グンゼ江南工場　　[生徒: 1-5-24・2-1-29・2-1-32・2-3-12・2-3-15]</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>学校から 2.8km</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
           <t>保育</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2社目</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>江南市立宮田東保育園　　[生徒: 1-5-1・1-5-25]</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>前より 1.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>教員 3　計 2社 / 7名</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>計 8.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="15" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  1社目</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園　　[生徒: 2-4-22]</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>学校から 1.6km</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>製造工業</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>福玉ロジスティクス株式会社　大口センター　　[生徒: 2-4-18・2-4-25]</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>学校から 2.1km</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  2社目</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>グンゼ江南工場　　[生徒: 1-5-24・2-1-29・2-1-32・2-3-12・2-3-15]</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>前より 1.3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>保育</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3社目</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>江南市立宮田東保育園　　[生徒: 1-5-1・1-5-25]</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>前より 1.3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>株式会社メイコン　本社　　[生徒: 2-1-14・2-2-6・2-4-24]</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>前より 2.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>教員 3　計 3社 / 8名</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr"/>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>計 8.4km</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="15" t="inlineStr"/>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1社目</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>福玉ロジスティクス株式会社　大口センター　　[生徒: 2-4-18・2-4-25]</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>学校から 2.1km</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="21" t="n"/>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2社目</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>株式会社メイコン　本社　　[生徒: 2-1-14・2-2-6・2-4-24]</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>前より 2.5km</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>教員 4　計 2社 / 5名</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr"/>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr"/>
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>計 9.2km</t>
         </is>
@@ -3782,16 +3756,16 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A14"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3817,7 +3791,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>見回り担当表　8/24(月)　(8社 / 14名)</t>
+          <t>見回り担当表　8/24(月)　(8社 / 15名)</t>
         </is>
       </c>
     </row>
@@ -3893,11 +3867,11 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園　　[生徒: 2-4-5・2-4-26]</t>
+          <t>江南市立古知野東保育園　　[生徒: 2-4-5・2-4-22・2-4-26]</t>
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
@@ -3939,7 +3913,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>教員 1　計 3社 / 6名</t>
+          <t>教員 1　計 3社 / 7名</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr"/>
